--- a/input/timetable/Государственное и муниципальное управление.xlsx
+++ b/input/timetable/Государственное и муниципальное управление.xlsx
@@ -140,12 +140,6 @@
     <t>Стратегическое управление (лек), К504</t>
   </si>
   <si>
-    <t>Организация государственных и муниципальных закупок (лек), К505</t>
-  </si>
-  <si>
-    <t>Организация государственных и муниципальных закупок (пр), К505</t>
-  </si>
-  <si>
     <t xml:space="preserve">
 Психология инклюзивного общества (лекция 16 ч)
 </t>
@@ -250,9 +244,6 @@
     <t>Теория государственного и муниципального управления (пр), К504</t>
   </si>
   <si>
-    <t>Русский язык и культура речи (пр), К504</t>
-  </si>
-  <si>
     <t>Теория государственного и муниципального управления (лек), К504//</t>
   </si>
   <si>
@@ -337,12 +328,6 @@
     <t>Основы муниципального управления и местного самоуправления (пр), К507</t>
   </si>
   <si>
-    <t>Современные технологии в государственном и муниципальном управлении (пр), К507</t>
-  </si>
-  <si>
-    <t>Современные технологии в государственном и муниципальном управлении  (пр), К507</t>
-  </si>
-  <si>
     <t>Противодействие экстремизму (лек), К429</t>
   </si>
   <si>
@@ -362,6 +347,21 @@
   </si>
   <si>
     <t>ФТД: Цифровая грамотность (пр), К518</t>
+  </si>
+  <si>
+    <t>Организация государственных и муниципальных закупок (лек), К428</t>
+  </si>
+  <si>
+    <t>Организация государственных и муниципальных закупок (пр), К428</t>
+  </si>
+  <si>
+    <t>Современные технологии в государственном и муниципальном управлении (пр), К508</t>
+  </si>
+  <si>
+    <t>Современные технологии в государственном и муниципальном управлении  (пр), К508</t>
+  </si>
+  <si>
+    <t>Русский язык и культура речи (пр), К413</t>
   </si>
 </sst>
 </file>
@@ -1183,7 +1183,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="295">
+  <cellXfs count="292">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1600,33 +1600,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1639,6 +1612,30 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1674,6 +1671,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1792,15 +1792,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2279,7 +2270,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
@@ -2295,14 +2286,14 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
@@ -2310,7 +2301,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
@@ -2344,7 +2335,7 @@
       </c>
       <c r="D7" s="72"/>
       <c r="E7" s="48" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
@@ -2355,7 +2346,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="88" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D8" s="88"/>
       <c r="E8" s="88"/>
@@ -2393,7 +2384,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="76" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D11" s="77"/>
       <c r="E11" s="77"/>
@@ -2405,7 +2396,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="79" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D12" s="80"/>
       <c r="E12" s="80"/>
@@ -2417,7 +2408,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="89" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D13" s="90"/>
       <c r="E13" s="90"/>
@@ -2433,7 +2424,7 @@
       <c r="C14" s="98"/>
       <c r="D14" s="99"/>
       <c r="E14" s="100" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F14" s="101"/>
     </row>
@@ -2443,11 +2434,11 @@
         <v>2</v>
       </c>
       <c r="C15" s="92" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D15" s="93"/>
       <c r="E15" s="93" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F15" s="94"/>
     </row>
@@ -2457,7 +2448,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="82" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D16" s="83"/>
       <c r="E16" s="83"/>
@@ -2479,7 +2470,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="73" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D18" s="74"/>
       <c r="E18" s="74"/>
@@ -2493,7 +2484,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="69" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D19" s="70"/>
       <c r="E19" s="70"/>
@@ -2505,7 +2496,7 @@
         <v>2</v>
       </c>
       <c r="C20" s="82" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D20" s="83"/>
       <c r="E20" s="83"/>
@@ -2517,7 +2508,7 @@
         <v>3</v>
       </c>
       <c r="C21" s="82" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D21" s="83"/>
       <c r="E21" s="96"/>
@@ -2575,7 +2566,7 @@
         <v>5</v>
       </c>
       <c r="C26" s="120" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D26" s="121"/>
       <c r="E26" s="121"/>
@@ -2599,7 +2590,7 @@
         <v>3</v>
       </c>
       <c r="C28" s="119" t="s">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="D28" s="108"/>
       <c r="E28" s="108"/>
@@ -2611,7 +2602,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="126" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D29" s="127"/>
       <c r="E29" s="127"/>
@@ -2645,7 +2636,7 @@
         <v>2</v>
       </c>
       <c r="C32" s="113" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D32" s="114"/>
       <c r="E32" s="114"/>
@@ -2709,7 +2700,7 @@
         <v>30</v>
       </c>
       <c r="C38" s="113" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D38" s="114"/>
       <c r="E38" s="114"/>
@@ -2721,7 +2712,7 @@
         <v>30</v>
       </c>
       <c r="C39" s="102" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D39" s="103"/>
       <c r="E39" s="103"/>
@@ -2740,7 +2731,7 @@
         <v>14</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2832,7 +2823,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
@@ -2848,14 +2839,14 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
@@ -2863,7 +2854,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
@@ -2892,12 +2883,12 @@
       <c r="A7" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="188" t="s">
+      <c r="C7" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="188"/>
+      <c r="D7" s="185"/>
       <c r="E7" s="50" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
@@ -2907,23 +2898,23 @@
       <c r="A8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="189" t="s">
+      <c r="C8" s="186" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="189"/>
-      <c r="E8" s="189"/>
-      <c r="F8" s="189"/>
+      <c r="D8" s="186"/>
+      <c r="E8" s="186"/>
+      <c r="F8" s="186"/>
     </row>
     <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="191" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="191"/>
-      <c r="E9" s="190"/>
-      <c r="F9" s="190"/>
+      <c r="C9" s="188" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="188"/>
+      <c r="E9" s="187"/>
+      <c r="F9" s="187"/>
     </row>
     <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="19" t="s">
@@ -2946,40 +2937,40 @@
       <c r="B11" s="26">
         <v>1</v>
       </c>
-      <c r="C11" s="182"/>
-      <c r="D11" s="183"/>
-      <c r="E11" s="183"/>
-      <c r="F11" s="184"/>
+      <c r="C11" s="171"/>
+      <c r="D11" s="172"/>
+      <c r="E11" s="172"/>
+      <c r="F11" s="173"/>
     </row>
     <row r="12" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="27"/>
       <c r="B12" s="28">
         <v>2</v>
       </c>
-      <c r="C12" s="185"/>
-      <c r="D12" s="186"/>
-      <c r="E12" s="186"/>
-      <c r="F12" s="187"/>
+      <c r="C12" s="182"/>
+      <c r="D12" s="183"/>
+      <c r="E12" s="183"/>
+      <c r="F12" s="184"/>
     </row>
     <row r="13" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="27"/>
       <c r="B13" s="28">
         <v>3</v>
       </c>
-      <c r="C13" s="192" t="s">
+      <c r="C13" s="189" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="193"/>
-      <c r="E13" s="193"/>
-      <c r="F13" s="194"/>
+      <c r="D13" s="190"/>
+      <c r="E13" s="190"/>
+      <c r="F13" s="191"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="29"/>
       <c r="B14" s="30"/>
-      <c r="C14" s="195"/>
-      <c r="D14" s="196"/>
-      <c r="E14" s="196"/>
-      <c r="F14" s="197"/>
+      <c r="C14" s="192"/>
+      <c r="D14" s="193"/>
+      <c r="E14" s="193"/>
+      <c r="F14" s="194"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="31" t="s">
@@ -2988,12 +2979,12 @@
       <c r="B15" s="32">
         <v>1</v>
       </c>
-      <c r="C15" s="171" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15" s="172"/>
-      <c r="E15" s="172"/>
-      <c r="F15" s="173"/>
+      <c r="C15" s="195" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="196"/>
+      <c r="E15" s="196"/>
+      <c r="F15" s="197"/>
     </row>
     <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="27"/>
@@ -3001,7 +2992,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="113" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D16" s="114"/>
       <c r="E16" s="114"/>
@@ -3013,7 +3004,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="135" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D17" s="136"/>
       <c r="E17" s="136"/>
@@ -3024,10 +3015,10 @@
       <c r="B18" s="30">
         <v>4</v>
       </c>
-      <c r="C18" s="168"/>
-      <c r="D18" s="169"/>
-      <c r="E18" s="169"/>
-      <c r="F18" s="170"/>
+      <c r="C18" s="174"/>
+      <c r="D18" s="175"/>
+      <c r="E18" s="175"/>
+      <c r="F18" s="176"/>
     </row>
     <row r="19" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="31" t="s">
@@ -3036,12 +3027,12 @@
       <c r="B19" s="32">
         <v>1</v>
       </c>
-      <c r="C19" s="176" t="s">
-        <v>81</v>
-      </c>
-      <c r="D19" s="177"/>
-      <c r="E19" s="177"/>
-      <c r="F19" s="178"/>
+      <c r="C19" s="179" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="180"/>
+      <c r="E19" s="180"/>
+      <c r="F19" s="181"/>
     </row>
     <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="27"/>
@@ -3049,11 +3040,11 @@
         <v>2</v>
       </c>
       <c r="C20" s="113" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" s="174"/>
-      <c r="E20" s="175" t="s">
-        <v>82</v>
+        <v>64</v>
+      </c>
+      <c r="D20" s="177"/>
+      <c r="E20" s="178" t="s">
+        <v>79</v>
       </c>
       <c r="F20" s="115"/>
     </row>
@@ -3084,20 +3075,20 @@
       <c r="B23" s="32">
         <v>1</v>
       </c>
-      <c r="C23" s="182"/>
-      <c r="D23" s="183"/>
-      <c r="E23" s="183"/>
-      <c r="F23" s="184"/>
+      <c r="C23" s="171"/>
+      <c r="D23" s="172"/>
+      <c r="E23" s="172"/>
+      <c r="F23" s="173"/>
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="27"/>
       <c r="B24" s="28">
         <v>2</v>
       </c>
-      <c r="C24" s="179"/>
-      <c r="D24" s="180"/>
-      <c r="E24" s="180"/>
-      <c r="F24" s="181"/>
+      <c r="C24" s="168"/>
+      <c r="D24" s="169"/>
+      <c r="E24" s="169"/>
+      <c r="F24" s="170"/>
     </row>
     <row r="25" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="33"/>
@@ -3129,7 +3120,7 @@
         <v>3</v>
       </c>
       <c r="C27" s="82" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D27" s="83"/>
       <c r="E27" s="83"/>
@@ -3141,7 +3132,7 @@
         <v>4</v>
       </c>
       <c r="C28" s="82" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D28" s="83"/>
       <c r="E28" s="83"/>
@@ -3153,7 +3144,7 @@
         <v>5</v>
       </c>
       <c r="C29" s="159" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D29" s="160"/>
       <c r="E29" s="160"/>
@@ -3167,7 +3158,7 @@
         <v>1</v>
       </c>
       <c r="C30" s="150" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
       <c r="D30" s="151"/>
       <c r="E30" s="151"/>
@@ -3179,7 +3170,7 @@
         <v>2</v>
       </c>
       <c r="C31" s="113" t="s">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="D31" s="114"/>
       <c r="E31" s="114"/>
@@ -3219,7 +3210,7 @@
         <v>30</v>
       </c>
       <c r="C35" s="165" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D35" s="166"/>
       <c r="E35" s="166"/>
@@ -3262,7 +3253,7 @@
         <v>14</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -3276,13 +3267,13 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C15:F15"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="C19:F19"/>
@@ -3355,7 +3346,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="66"/>
@@ -3379,14 +3370,14 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="68" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
@@ -3394,7 +3385,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
@@ -3438,19 +3429,19 @@
       <c r="A8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="189" t="s">
+      <c r="C8" s="186" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="189"/>
-      <c r="E8" s="189"/>
-      <c r="F8" s="189"/>
+      <c r="D8" s="186"/>
+      <c r="E8" s="186"/>
+      <c r="F8" s="186"/>
     </row>
     <row r="9" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="208" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D9" s="208"/>
       <c r="E9" s="208"/>
@@ -3478,7 +3469,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="205" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D11" s="206"/>
       <c r="E11" s="206"/>
@@ -3489,34 +3480,34 @@
       <c r="B12" s="28">
         <v>4</v>
       </c>
-      <c r="C12" s="192" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" s="193"/>
-      <c r="E12" s="193"/>
-      <c r="F12" s="194"/>
+      <c r="C12" s="189" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" s="190"/>
+      <c r="E12" s="190"/>
+      <c r="F12" s="191"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="27"/>
       <c r="B13" s="28">
         <v>5</v>
       </c>
-      <c r="C13" s="192" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" s="193"/>
-      <c r="E13" s="193"/>
-      <c r="F13" s="194"/>
+      <c r="C13" s="189" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="190"/>
+      <c r="E13" s="190"/>
+      <c r="F13" s="191"/>
     </row>
     <row r="14" spans="1:6" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="31" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C14" s="204" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D14" s="100"/>
       <c r="E14" s="100"/>
@@ -3528,7 +3519,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="92" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D15" s="93"/>
       <c r="E15" s="93"/>
@@ -3540,7 +3531,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="113" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" s="114"/>
       <c r="E16" s="114"/>
@@ -3552,7 +3543,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="209" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D17" s="210"/>
       <c r="E17" s="210"/>
@@ -3578,7 +3569,7 @@
       <c r="C19" s="198"/>
       <c r="D19" s="199"/>
       <c r="E19" s="200" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F19" s="201"/>
     </row>
@@ -3588,7 +3579,7 @@
         <v>3</v>
       </c>
       <c r="C20" s="82" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D20" s="83"/>
       <c r="E20" s="83"/>
@@ -3612,7 +3603,7 @@
         <v>2</v>
       </c>
       <c r="C22" s="218" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D22" s="219"/>
       <c r="E22" s="219"/>
@@ -3623,12 +3614,12 @@
       <c r="B23" s="28">
         <v>3</v>
       </c>
-      <c r="C23" s="192" t="s">
-        <v>95</v>
-      </c>
-      <c r="D23" s="193"/>
-      <c r="E23" s="193"/>
-      <c r="F23" s="194"/>
+      <c r="C23" s="189" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" s="190"/>
+      <c r="E23" s="190"/>
+      <c r="F23" s="191"/>
     </row>
     <row r="24" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="27"/>
@@ -3636,7 +3627,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="92" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D24" s="93"/>
       <c r="E24" s="93"/>
@@ -3670,7 +3661,7 @@
         <v>4</v>
       </c>
       <c r="C27" s="113" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D27" s="114"/>
       <c r="E27" s="114"/>
@@ -3682,7 +3673,7 @@
         <v>5</v>
       </c>
       <c r="C28" s="113" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D28" s="114"/>
       <c r="E28" s="114"/>
@@ -3694,7 +3685,7 @@
         <v>6</v>
       </c>
       <c r="C29" s="227" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D29" s="228"/>
       <c r="E29" s="228"/>
@@ -3708,7 +3699,7 @@
         <v>2</v>
       </c>
       <c r="C30" s="230" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D30" s="231"/>
       <c r="E30" s="231"/>
@@ -3720,7 +3711,7 @@
         <v>3</v>
       </c>
       <c r="C31" s="113" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D31" s="233"/>
       <c r="E31" s="233"/>
@@ -3760,7 +3751,7 @@
         <v>30</v>
       </c>
       <c r="C35" s="221" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D35" s="222"/>
       <c r="E35" s="222"/>
@@ -3768,11 +3759,11 @@
     </row>
     <row r="36" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="63" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B36" s="64"/>
       <c r="C36" s="202" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D36" s="202"/>
       <c r="E36" s="202"/>
@@ -3791,7 +3782,7 @@
         <v>14</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -3886,7 +3877,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
@@ -3902,14 +3893,14 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
@@ -3917,7 +3908,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
@@ -3946,12 +3937,12 @@
       <c r="A7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="253" t="s">
+      <c r="C7" s="250" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="253"/>
+      <c r="D7" s="250"/>
       <c r="E7" s="15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
@@ -3961,19 +3952,19 @@
       <c r="A8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="189" t="s">
+      <c r="C8" s="186" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="189"/>
-      <c r="E8" s="189"/>
-      <c r="F8" s="189"/>
+      <c r="D8" s="186"/>
+      <c r="E8" s="186"/>
+      <c r="F8" s="186"/>
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
@@ -4000,10 +3991,10 @@
       <c r="B11" s="26">
         <v>1</v>
       </c>
-      <c r="C11" s="260"/>
-      <c r="D11" s="261"/>
+      <c r="C11" s="257"/>
+      <c r="D11" s="258"/>
       <c r="E11" s="206" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F11" s="207"/>
     </row>
@@ -4013,7 +4004,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="126" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D12" s="127"/>
       <c r="E12" s="127"/>
@@ -4024,24 +4015,24 @@
       <c r="B13" s="28">
         <v>3</v>
       </c>
-      <c r="C13" s="257" t="s">
-        <v>100</v>
-      </c>
-      <c r="D13" s="258"/>
-      <c r="E13" s="258"/>
-      <c r="F13" s="259"/>
+      <c r="C13" s="254" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" s="255"/>
+      <c r="E13" s="255"/>
+      <c r="F13" s="256"/>
     </row>
     <row r="14" spans="1:6" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="27"/>
       <c r="B14" s="28">
         <v>4</v>
       </c>
-      <c r="C14" s="262" t="s">
-        <v>101</v>
-      </c>
-      <c r="D14" s="263"/>
-      <c r="E14" s="264"/>
-      <c r="F14" s="265"/>
+      <c r="C14" s="259" t="s">
+        <v>98</v>
+      </c>
+      <c r="D14" s="260"/>
+      <c r="E14" s="261"/>
+      <c r="F14" s="262"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="31" t="s">
@@ -4050,10 +4041,10 @@
       <c r="B15" s="32">
         <v>2</v>
       </c>
-      <c r="C15" s="254"/>
-      <c r="D15" s="255"/>
-      <c r="E15" s="255"/>
-      <c r="F15" s="256"/>
+      <c r="C15" s="251"/>
+      <c r="D15" s="252"/>
+      <c r="E15" s="252"/>
+      <c r="F15" s="253"/>
     </row>
     <row r="16" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="27"/>
@@ -4061,7 +4052,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="126" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D16" s="127"/>
       <c r="E16" s="127"/>
@@ -4073,7 +4064,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="241" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D17" s="242"/>
       <c r="E17" s="242"/>
@@ -4085,67 +4076,67 @@
         <v>5</v>
       </c>
       <c r="C18" s="241" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D18" s="242"/>
-      <c r="E18" s="266"/>
-      <c r="F18" s="267"/>
+      <c r="E18" s="263"/>
+      <c r="F18" s="264"/>
     </row>
     <row r="19" spans="1:6" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="33"/>
       <c r="B19" s="30">
         <v>6</v>
       </c>
-      <c r="C19" s="285"/>
-      <c r="D19" s="286"/>
-      <c r="E19" s="268"/>
-      <c r="F19" s="269"/>
+      <c r="C19" s="282"/>
+      <c r="D19" s="283"/>
+      <c r="E19" s="265"/>
+      <c r="F19" s="266"/>
     </row>
     <row r="20" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="31" t="s">
         <v>21</v>
       </c>
       <c r="B20" s="32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" s="244"/>
       <c r="D20" s="245"/>
       <c r="E20" s="245"/>
       <c r="F20" s="246"/>
     </row>
-    <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="27"/>
       <c r="B21" s="28">
-        <v>3</v>
-      </c>
-      <c r="C21" s="247"/>
-      <c r="D21" s="248"/>
-      <c r="E21" s="248"/>
-      <c r="F21" s="249"/>
+        <v>2</v>
+      </c>
+      <c r="C21" s="241" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="242"/>
+      <c r="E21" s="242"/>
+      <c r="F21" s="243"/>
     </row>
     <row r="22" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="27"/>
       <c r="B22" s="28">
-        <v>4</v>
-      </c>
-      <c r="C22" s="250" t="s">
-        <v>103</v>
-      </c>
-      <c r="D22" s="251"/>
-      <c r="E22" s="251"/>
-      <c r="F22" s="252"/>
-    </row>
-    <row r="23" spans="1:6" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="C22" s="247" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" s="248"/>
+      <c r="E22" s="248"/>
+      <c r="F22" s="249"/>
+    </row>
+    <row r="23" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="27"/>
       <c r="B23" s="28">
-        <v>5</v>
-      </c>
-      <c r="C23" s="276" t="s">
-        <v>104</v>
-      </c>
-      <c r="D23" s="277"/>
-      <c r="E23" s="277"/>
-      <c r="F23" s="278"/>
+        <v>4</v>
+      </c>
+      <c r="C23" s="273"/>
+      <c r="D23" s="274"/>
+      <c r="E23" s="274"/>
+      <c r="F23" s="275"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" s="31" t="s">
@@ -4155,7 +4146,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="238" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D24" s="239"/>
       <c r="E24" s="239"/>
@@ -4167,7 +4158,7 @@
         <v>2</v>
       </c>
       <c r="C25" s="76" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D25" s="77"/>
       <c r="E25" s="77"/>
@@ -4178,24 +4169,24 @@
       <c r="B26" s="28">
         <v>3</v>
       </c>
-      <c r="C26" s="257" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" s="258"/>
-      <c r="E26" s="258"/>
-      <c r="F26" s="259"/>
+      <c r="C26" s="254" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" s="255"/>
+      <c r="E26" s="255"/>
+      <c r="F26" s="256"/>
     </row>
     <row r="27" spans="1:6" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="33"/>
       <c r="B27" s="30">
         <v>4</v>
       </c>
-      <c r="C27" s="276" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" s="277"/>
-      <c r="E27" s="277"/>
-      <c r="F27" s="278"/>
+      <c r="C27" s="273" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" s="274"/>
+      <c r="E27" s="274"/>
+      <c r="F27" s="275"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" s="31" t="s">
@@ -4204,20 +4195,20 @@
       <c r="B28" s="32">
         <v>4</v>
       </c>
-      <c r="C28" s="279"/>
-      <c r="D28" s="280"/>
-      <c r="E28" s="280"/>
-      <c r="F28" s="281"/>
+      <c r="C28" s="276"/>
+      <c r="D28" s="277"/>
+      <c r="E28" s="277"/>
+      <c r="F28" s="278"/>
     </row>
     <row r="29" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="34"/>
       <c r="B29" s="28">
         <v>5</v>
       </c>
-      <c r="C29" s="293"/>
-      <c r="D29" s="294"/>
+      <c r="C29" s="290"/>
+      <c r="D29" s="291"/>
       <c r="E29" s="127" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F29" s="128"/>
     </row>
@@ -4226,18 +4217,18 @@
       <c r="B30" s="28">
         <v>6</v>
       </c>
-      <c r="C30" s="293"/>
-      <c r="D30" s="294"/>
+      <c r="C30" s="290"/>
+      <c r="D30" s="291"/>
       <c r="E30" s="127"/>
       <c r="F30" s="128"/>
     </row>
     <row r="31" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="36"/>
       <c r="B31" s="30"/>
-      <c r="C31" s="282"/>
-      <c r="D31" s="283"/>
-      <c r="E31" s="283"/>
-      <c r="F31" s="284"/>
+      <c r="C31" s="279"/>
+      <c r="D31" s="280"/>
+      <c r="E31" s="280"/>
+      <c r="F31" s="281"/>
     </row>
     <row r="32" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="55" t="s">
@@ -4246,42 +4237,42 @@
       <c r="B32" s="26">
         <v>4</v>
       </c>
-      <c r="C32" s="287" t="s">
-        <v>108</v>
-      </c>
-      <c r="D32" s="288"/>
-      <c r="E32" s="288"/>
-      <c r="F32" s="289"/>
+      <c r="C32" s="284" t="s">
+        <v>103</v>
+      </c>
+      <c r="D32" s="285"/>
+      <c r="E32" s="285"/>
+      <c r="F32" s="286"/>
     </row>
     <row r="33" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="38"/>
       <c r="B33" s="28">
         <v>5</v>
       </c>
-      <c r="C33" s="290" t="s">
-        <v>109</v>
-      </c>
-      <c r="D33" s="291"/>
-      <c r="E33" s="291"/>
-      <c r="F33" s="292"/>
+      <c r="C33" s="287" t="s">
+        <v>104</v>
+      </c>
+      <c r="D33" s="288"/>
+      <c r="E33" s="288"/>
+      <c r="F33" s="289"/>
     </row>
     <row r="34" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="38"/>
       <c r="B34" s="28">
         <v>6</v>
       </c>
-      <c r="C34" s="270"/>
-      <c r="D34" s="271"/>
-      <c r="E34" s="271"/>
-      <c r="F34" s="272"/>
+      <c r="C34" s="267"/>
+      <c r="D34" s="268"/>
+      <c r="E34" s="268"/>
+      <c r="F34" s="269"/>
     </row>
     <row r="35" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="52"/>
       <c r="B35" s="56"/>
-      <c r="C35" s="273"/>
-      <c r="D35" s="274"/>
-      <c r="E35" s="274"/>
-      <c r="F35" s="275"/>
+      <c r="C35" s="270"/>
+      <c r="D35" s="271"/>
+      <c r="E35" s="271"/>
+      <c r="F35" s="272"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
@@ -4296,7 +4287,7 @@
         <v>14</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/input/timetable/Государственное и муниципальное управление.xlsx
+++ b/input/timetable/Государственное и муниципальное управление.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28560" windowHeight="13380" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28560" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="148">
   <si>
     <t>пара</t>
   </si>
@@ -71,6 +71,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -128,16 +131,43 @@
     <t>Русский язык и культура речи (лек 32 ч)</t>
   </si>
   <si>
+    <t>Имамвердиева М.И.</t>
+  </si>
+  <si>
+    <t>Гардт А.А.</t>
+  </si>
+  <si>
     <t>Философия (лек 32 ч)</t>
   </si>
   <si>
     <t>Работа в команде (лек 32 ч)</t>
   </si>
   <si>
+    <t>Арапова Л.Ш.</t>
+  </si>
+  <si>
+    <t>Ищенко О.В.</t>
+  </si>
+  <si>
     <t>405-31</t>
   </si>
   <si>
+    <t>Лешукова Е.В.</t>
+  </si>
+  <si>
+    <t>Вариясова Е.В.</t>
+  </si>
+  <si>
+    <t>Евсеенко Е.А.</t>
+  </si>
+  <si>
     <t>Стратегическое управление (лек), К504</t>
+  </si>
+  <si>
+    <t>Сергеева И.В.</t>
+  </si>
+  <si>
+    <t>Малагин Д.В.</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -145,15 +175,30 @@
 </t>
   </si>
   <si>
+    <t>Усаева Н.Р.</t>
+  </si>
+  <si>
     <t>405-41</t>
   </si>
   <si>
+    <t>Замятина М.С.</t>
+  </si>
+  <si>
     <t>История России (лекция 32 ч)</t>
   </si>
   <si>
+    <t>Литовченко А.С.</t>
+  </si>
+  <si>
+    <t>Биек А.В.</t>
+  </si>
+  <si>
     <t>ФТД: Цифровая грамотность  (лек 16 ч)</t>
   </si>
   <si>
+    <t>Осипова А.В.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Примечание: *  </t>
   </si>
   <si>
@@ -166,6 +211,9 @@
     <t>Элективные дисциплины по физической культуре и спорту, С*</t>
   </si>
   <si>
+    <t>Колесник А.А.</t>
+  </si>
+  <si>
     <t>Иностранный язык в проф. сфере (24ч), п/г 2, К509</t>
   </si>
   <si>
@@ -211,15 +259,33 @@
     <t>02.02.2026-01.04.2026</t>
   </si>
   <si>
+    <t>Муртазин Ш.Н.</t>
+  </si>
+  <si>
+    <t>Галлямова Л.В.</t>
+  </si>
+  <si>
+    <t>Байбулатов Р.Я.</t>
+  </si>
+  <si>
     <t>Инф. технологии обработки деловой информации, п/г 1, К518</t>
   </si>
   <si>
     <t>Инф. технологии обработки деловой информации, п/г 2, К518</t>
   </si>
   <si>
+    <t>Кучин И.А.; Царская Т.С.</t>
+  </si>
+  <si>
     <t>Иностранный язык, п/г 2, К509</t>
   </si>
   <si>
+    <t>Шайторова И.А.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Кучин И.А.</t>
+  </si>
+  <si>
     <t>Иностранный язык, п/г 1, К526</t>
   </si>
   <si>
@@ -250,9 +316,33 @@
     <t>Стратегическое управление (пр), К504</t>
   </si>
   <si>
+    <t>Бутенко Н.А.</t>
+  </si>
+  <si>
+    <t>Калинина Е.А.</t>
+  </si>
+  <si>
     <t>Основы проектной деятельности (лек 16 ч)</t>
   </si>
   <si>
+    <t>Плесовских И.Н.</t>
+  </si>
+  <si>
+    <t>Литовченко А.С.;Кузнецова С.В.</t>
+  </si>
+  <si>
+    <t>Кручинина В.А./Осипова А.В.</t>
+  </si>
+  <si>
+    <t>Мордвинцева А.Ю.</t>
+  </si>
+  <si>
+    <t>Ищенко О.В./Биек А.В.</t>
+  </si>
+  <si>
+    <t>Биек А.В./Осипова А.В.</t>
+  </si>
+  <si>
     <t>Основы проектной деятельности (пр), К505</t>
   </si>
   <si>
@@ -271,6 +361,15 @@
     <t>// Философия (пр), К412</t>
   </si>
   <si>
+    <t>Кислова Н.А.</t>
+  </si>
+  <si>
+    <t>Мордвинцева А.Ю./Колесник А.А.</t>
+  </si>
+  <si>
+    <t>Куприянова Е.В.</t>
+  </si>
+  <si>
     <t>Технологии проведения совещаний и переговоров (лек)/(пр), К505</t>
   </si>
   <si>
@@ -280,6 +379,9 @@
     <t>Управленческие конфликты (лек), К506</t>
   </si>
   <si>
+    <t>Усаева Н.Р./Жадобина Н.Н.</t>
+  </si>
+  <si>
     <t>Психология инклюзивного общества (пр), К505// Муниципальное право (лек), К505</t>
   </si>
   <si>
@@ -314,6 +416,12 @@
   </si>
   <si>
     <t>Основы информационно-аналитической деятельности в муниципальном управлении, п/г 1, К518</t>
+  </si>
+  <si>
+    <t>Сметанина Г.А.</t>
+  </si>
+  <si>
+    <t>Лукиянчина Е.В.</t>
   </si>
   <si>
     <t>Основы муниципального управления и местного самоуправления (лек). К506</t>
@@ -473,7 +581,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -492,6 +600,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -503,7 +617,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="55">
+  <borders count="63">
     <border>
       <left/>
       <right/>
@@ -624,6 +738,64 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -662,6 +834,19 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -832,6 +1017,19 @@
     </border>
     <border>
       <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -1121,16 +1319,42 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1183,7 +1407,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="292">
+  <cellXfs count="316">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1227,30 +1451,34 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1275,7 +1503,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1283,20 +1511,21 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -1311,7 +1540,9 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
@@ -1319,21 +1550,27 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="15" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1341,7 +1578,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1351,25 +1588,152 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1378,38 +1742,217 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1420,513 +1963,232 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2249,7 +2511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2257,10 +2519,11 @@
     <col min="3" max="3" width="19" style="2" customWidth="1"/>
     <col min="4" max="4" width="18.5703125" style="2" customWidth="1"/>
     <col min="5" max="6" width="18.42578125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -2268,15 +2531,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -2284,77 +2547,77 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="17"/>
-      <c r="E6" s="47">
+      <c r="E6" s="50">
         <v>1</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="140" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="72"/>
-      <c r="E7" s="48" t="s">
-        <v>56</v>
+      <c r="D7" s="140"/>
+      <c r="E7" s="51" t="s">
+        <v>72</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="88" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="88"/>
-      <c r="E8" s="88"/>
-      <c r="F8" s="88"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="153" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="153"/>
+      <c r="E8" s="153"/>
+      <c r="F8" s="153"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="20" t="s">
         <v>0</v>
@@ -2365,377 +2628,471 @@
       <c r="D9" s="22"/>
       <c r="E9" s="23"/>
       <c r="F9" s="24"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="26">
+      <c r="G9" s="25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="27">
         <v>1</v>
       </c>
-      <c r="C10" s="85"/>
-      <c r="D10" s="86"/>
-      <c r="E10" s="86"/>
-      <c r="F10" s="87"/>
-    </row>
-    <row r="11" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="27"/>
-      <c r="B11" s="28">
+      <c r="C10" s="150"/>
+      <c r="D10" s="151"/>
+      <c r="E10" s="151"/>
+      <c r="F10" s="152"/>
+      <c r="G10" s="28"/>
+    </row>
+    <row r="11" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="29"/>
+      <c r="B11" s="30">
         <v>2</v>
       </c>
-      <c r="C11" s="76" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="78"/>
-    </row>
-    <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28">
+      <c r="C11" s="144" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="145"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="146"/>
+      <c r="G11" s="83" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="29"/>
+      <c r="B12" s="30">
         <v>3</v>
       </c>
-      <c r="C12" s="79" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" s="80"/>
-      <c r="E12" s="80"/>
-      <c r="F12" s="81"/>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="27"/>
-      <c r="B13" s="28">
+      <c r="C12" s="147" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="148"/>
+      <c r="E12" s="148"/>
+      <c r="F12" s="149"/>
+      <c r="G12" s="83" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="29"/>
+      <c r="B13" s="30">
         <v>4</v>
       </c>
-      <c r="C13" s="89" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" s="90"/>
-      <c r="E13" s="90"/>
-      <c r="F13" s="91"/>
-    </row>
-    <row r="14" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="32">
+      <c r="C13" s="154" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="155"/>
+      <c r="E13" s="155"/>
+      <c r="F13" s="156"/>
+      <c r="G13" s="79" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="34">
         <v>1</v>
       </c>
-      <c r="C14" s="98"/>
-      <c r="D14" s="99"/>
-      <c r="E14" s="100" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" s="101"/>
-    </row>
-    <row r="15" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="27"/>
-      <c r="B15" s="28">
+      <c r="C14" s="161"/>
+      <c r="D14" s="162"/>
+      <c r="E14" s="163" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" s="164"/>
+      <c r="G14" s="80" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="29"/>
+      <c r="B15" s="30">
         <v>2</v>
       </c>
-      <c r="C15" s="92" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="93"/>
-      <c r="E15" s="93" t="s">
-        <v>63</v>
-      </c>
-      <c r="F15" s="94"/>
-    </row>
-    <row r="16" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="27"/>
-      <c r="B16" s="28">
+      <c r="C15" s="157" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="158"/>
+      <c r="E15" s="158" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" s="159"/>
+      <c r="G15" s="79" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="29"/>
+      <c r="B16" s="30">
         <v>3</v>
       </c>
-      <c r="C16" s="82" t="s">
-        <v>106</v>
-      </c>
-      <c r="D16" s="83"/>
-      <c r="E16" s="83"/>
-      <c r="F16" s="84"/>
-    </row>
-    <row r="17" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="65"/>
-      <c r="B17" s="35">
+      <c r="C16" s="102" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16" s="103"/>
+      <c r="E16" s="103"/>
+      <c r="F16" s="104"/>
+      <c r="G16" s="79" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="74"/>
+      <c r="B17" s="37">
         <v>4</v>
       </c>
-      <c r="C17" s="95"/>
-      <c r="D17" s="96"/>
-      <c r="E17" s="96"/>
-      <c r="F17" s="97"/>
-    </row>
-    <row r="18" spans="1:6" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="33"/>
-      <c r="B18" s="30">
+      <c r="C17" s="160"/>
+      <c r="D17" s="129"/>
+      <c r="E17" s="129"/>
+      <c r="F17" s="130"/>
+      <c r="G17" s="79"/>
+    </row>
+    <row r="18" spans="1:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="35"/>
+      <c r="B18" s="32">
         <v>5</v>
       </c>
-      <c r="C18" s="73" t="s">
-        <v>105</v>
-      </c>
-      <c r="D18" s="74"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="75"/>
-    </row>
-    <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="32">
+      <c r="C18" s="141" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" s="142"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="143"/>
+      <c r="G18" s="79" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="34">
         <v>1</v>
       </c>
-      <c r="C19" s="69" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" s="70"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="71"/>
-    </row>
-    <row r="20" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="27"/>
-      <c r="B20" s="28">
+      <c r="C19" s="137" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19" s="138"/>
+      <c r="E19" s="138"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="80" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="29"/>
+      <c r="B20" s="30">
         <v>2</v>
       </c>
-      <c r="C20" s="82" t="s">
-        <v>65</v>
-      </c>
-      <c r="D20" s="83"/>
-      <c r="E20" s="83"/>
-      <c r="F20" s="84"/>
-    </row>
-    <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="27"/>
-      <c r="B21" s="28">
+      <c r="C20" s="102" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" s="103"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="104"/>
+      <c r="G20" s="79" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="29"/>
+      <c r="B21" s="30">
         <v>3</v>
       </c>
-      <c r="C21" s="82" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" s="83"/>
-      <c r="E21" s="96"/>
-      <c r="F21" s="97"/>
-    </row>
-    <row r="22" spans="1:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="33"/>
-      <c r="B22" s="30">
+      <c r="C21" s="102" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="103"/>
+      <c r="E21" s="129"/>
+      <c r="F21" s="130"/>
+      <c r="G21" s="79" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="35"/>
+      <c r="B22" s="32">
         <v>4</v>
       </c>
-      <c r="C22" s="102" t="s">
-        <v>26</v>
-      </c>
-      <c r="D22" s="103"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="104"/>
-    </row>
-    <row r="23" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="32">
+      <c r="C22" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="100"/>
+      <c r="E22" s="100"/>
+      <c r="F22" s="101"/>
+      <c r="G22" s="79" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="34">
         <v>2</v>
       </c>
-      <c r="C23" s="132"/>
-      <c r="D23" s="133"/>
-      <c r="E23" s="133"/>
-      <c r="F23" s="134"/>
-    </row>
-    <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="27"/>
-      <c r="B24" s="28">
+      <c r="C23" s="117"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="119"/>
+      <c r="G23" s="64"/>
+    </row>
+    <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="29"/>
+      <c r="B24" s="30">
         <v>3</v>
       </c>
-      <c r="C24" s="135"/>
-      <c r="D24" s="136"/>
-      <c r="E24" s="136"/>
-      <c r="F24" s="137"/>
-    </row>
-    <row r="25" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="27"/>
-      <c r="B25" s="28">
+      <c r="C24" s="120"/>
+      <c r="D24" s="121"/>
+      <c r="E24" s="121"/>
+      <c r="F24" s="122"/>
+      <c r="G24" s="82"/>
+    </row>
+    <row r="25" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="29"/>
+      <c r="B25" s="30">
         <v>4</v>
       </c>
-      <c r="C25" s="126" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="127"/>
-      <c r="E25" s="127"/>
-      <c r="F25" s="128"/>
-    </row>
-    <row r="26" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="33"/>
-      <c r="B26" s="30">
+      <c r="C25" s="111" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="112"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="113"/>
+      <c r="G25" s="79" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="35"/>
+      <c r="B26" s="32">
         <v>5</v>
       </c>
-      <c r="C26" s="120" t="s">
-        <v>67</v>
-      </c>
-      <c r="D26" s="121"/>
-      <c r="E26" s="121"/>
-      <c r="F26" s="122"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="32">
+      <c r="C26" s="105" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="106"/>
+      <c r="E26" s="106"/>
+      <c r="F26" s="107"/>
+      <c r="G26" s="82" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="34">
         <v>2</v>
       </c>
-      <c r="C27" s="123"/>
-      <c r="D27" s="124"/>
-      <c r="E27" s="124"/>
-      <c r="F27" s="125"/>
-    </row>
-    <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="34"/>
-      <c r="B28" s="28">
+      <c r="C27" s="108"/>
+      <c r="D27" s="109"/>
+      <c r="E27" s="109"/>
+      <c r="F27" s="110"/>
+      <c r="G27" s="64"/>
+    </row>
+    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="36"/>
+      <c r="B28" s="30">
         <v>3</v>
       </c>
-      <c r="C28" s="119" t="s">
-        <v>111</v>
-      </c>
-      <c r="D28" s="108"/>
-      <c r="E28" s="108"/>
-      <c r="F28" s="109"/>
-    </row>
-    <row r="29" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="34"/>
-      <c r="B29" s="28">
+      <c r="C28" s="96" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="97"/>
+      <c r="E28" s="97"/>
+      <c r="F28" s="98"/>
+      <c r="G28" s="79" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="36"/>
+      <c r="B29" s="30">
         <v>4</v>
       </c>
-      <c r="C29" s="126" t="s">
-        <v>72</v>
-      </c>
-      <c r="D29" s="127"/>
-      <c r="E29" s="127"/>
-      <c r="F29" s="128"/>
-    </row>
-    <row r="30" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="36"/>
-      <c r="B30" s="30">
+      <c r="C29" s="111" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" s="112"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="113"/>
+      <c r="G29" s="79" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="38"/>
+      <c r="B30" s="32">
         <v>5</v>
       </c>
-      <c r="C30" s="129"/>
-      <c r="D30" s="130"/>
-      <c r="E30" s="130"/>
-      <c r="F30" s="131"/>
-    </row>
-    <row r="31" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" s="32">
+      <c r="C30" s="114"/>
+      <c r="D30" s="115"/>
+      <c r="E30" s="115"/>
+      <c r="F30" s="116"/>
+      <c r="G30" s="79"/>
+    </row>
+    <row r="31" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="34">
         <v>1</v>
       </c>
-      <c r="C31" s="138"/>
-      <c r="D31" s="139"/>
-      <c r="E31" s="139"/>
-      <c r="F31" s="140"/>
-    </row>
-    <row r="32" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="38"/>
-      <c r="B32" s="28">
+      <c r="C31" s="123"/>
+      <c r="D31" s="124"/>
+      <c r="E31" s="124"/>
+      <c r="F31" s="125"/>
+      <c r="G31" s="80"/>
+    </row>
+    <row r="32" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="40"/>
+      <c r="B32" s="30">
         <v>2</v>
       </c>
-      <c r="C32" s="113" t="s">
-        <v>73</v>
-      </c>
-      <c r="D32" s="114"/>
-      <c r="E32" s="114"/>
-      <c r="F32" s="115"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="39"/>
-      <c r="B33" s="35">
+      <c r="C32" s="126" t="s">
+        <v>95</v>
+      </c>
+      <c r="D32" s="127"/>
+      <c r="E32" s="127"/>
+      <c r="F32" s="128"/>
+      <c r="G32" s="79" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="41"/>
+      <c r="B33" s="37">
         <v>3</v>
       </c>
-      <c r="C33" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="D33" s="108"/>
-      <c r="E33" s="108"/>
-      <c r="F33" s="109"/>
-    </row>
-    <row r="34" spans="1:6" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="40"/>
-      <c r="B34" s="30"/>
-      <c r="C34" s="116"/>
-      <c r="D34" s="117"/>
-      <c r="E34" s="117"/>
-      <c r="F34" s="118"/>
-    </row>
-    <row r="35" spans="1:6" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="41"/>
-      <c r="B35" s="42"/>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
-      <c r="E35" s="111"/>
-      <c r="F35" s="112"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="43"/>
-      <c r="B36" s="44" t="s">
+      <c r="C33" s="96" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="97"/>
+      <c r="E33" s="97"/>
+      <c r="F33" s="98"/>
+      <c r="G33" s="79" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="42"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="93"/>
+      <c r="D34" s="94"/>
+      <c r="E34" s="94"/>
+      <c r="F34" s="95"/>
+      <c r="G34" s="78"/>
+    </row>
+    <row r="35" spans="1:7" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="43"/>
+      <c r="B35" s="44"/>
+      <c r="C35" s="134"/>
+      <c r="D35" s="135"/>
+      <c r="E35" s="135"/>
+      <c r="F35" s="136"/>
+      <c r="G35" s="45"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="46"/>
+      <c r="B36" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="131" t="s">
         <v>30</v>
       </c>
-      <c r="C36" s="105" t="s">
-        <v>29</v>
-      </c>
-      <c r="D36" s="106"/>
-      <c r="E36" s="106"/>
-      <c r="F36" s="107"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" s="38"/>
-      <c r="B37" s="45" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="D37" s="108"/>
-      <c r="E37" s="108"/>
-      <c r="F37" s="109"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A38" s="39"/>
-      <c r="B38" s="58" t="s">
-        <v>30</v>
-      </c>
-      <c r="C38" s="113" t="s">
-        <v>40</v>
-      </c>
-      <c r="D38" s="114"/>
-      <c r="E38" s="114"/>
-      <c r="F38" s="115"/>
-    </row>
-    <row r="39" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="40"/>
-      <c r="B39" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="C39" s="102" t="s">
-        <v>41</v>
-      </c>
-      <c r="D39" s="103"/>
-      <c r="E39" s="103"/>
-      <c r="F39" s="104"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D36" s="132"/>
+      <c r="E36" s="132"/>
+      <c r="F36" s="133"/>
+      <c r="G36" s="80" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="40"/>
+      <c r="B37" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="102" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" s="97"/>
+      <c r="E37" s="97"/>
+      <c r="F37" s="98"/>
+      <c r="G37" s="79" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38" s="41"/>
+      <c r="B38" s="63" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" s="126" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="127"/>
+      <c r="E38" s="127"/>
+      <c r="F38" s="128"/>
+      <c r="G38" s="81" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="42"/>
+      <c r="B39" s="49" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="99" t="s">
+        <v>55</v>
+      </c>
+      <c r="D39" s="100"/>
+      <c r="E39" s="100"/>
+      <c r="F39" s="101"/>
+      <c r="G39" s="84" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C38:F38"/>
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C22:F22"/>
@@ -2752,25 +3109,6 @@
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="E21:F21"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -2801,7 +3139,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2810,10 +3148,11 @@
     <col min="4" max="4" width="18.85546875" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.85546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="20" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -2821,15 +3160,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -2837,39 +3176,39 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="57" t="s">
-        <v>16</v>
+      <c r="C6" s="62" t="s">
+        <v>17</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -2879,46 +3218,46 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="171" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="185"/>
-      <c r="E7" s="50" t="s">
-        <v>39</v>
+      <c r="D7" s="171"/>
+      <c r="E7" s="53" t="s">
+        <v>50</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="186" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="186"/>
-      <c r="E8" s="186"/>
-      <c r="F8" s="186"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>26</v>
+      </c>
+      <c r="C8" s="172" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="172"/>
+      <c r="E8" s="172"/>
+      <c r="F8" s="172"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="188" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" s="188"/>
-      <c r="E9" s="187"/>
-      <c r="F9" s="187"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>33</v>
+      </c>
+      <c r="C9" s="174" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="174"/>
+      <c r="E9" s="173"/>
+      <c r="F9" s="173"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="20" t="s">
         <v>0</v>
@@ -2929,354 +3268,391 @@
       <c r="D10" s="22"/>
       <c r="E10" s="23"/>
       <c r="F10" s="24"/>
-    </row>
-    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="26">
+      <c r="G10" s="25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="27">
         <v>1</v>
       </c>
-      <c r="C11" s="171"/>
-      <c r="D11" s="172"/>
-      <c r="E11" s="172"/>
-      <c r="F11" s="173"/>
-    </row>
-    <row r="12" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28">
+      <c r="C11" s="165"/>
+      <c r="D11" s="166"/>
+      <c r="E11" s="166"/>
+      <c r="F11" s="167"/>
+      <c r="G11" s="64"/>
+    </row>
+    <row r="12" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="29"/>
+      <c r="B12" s="30">
         <v>2</v>
       </c>
-      <c r="C12" s="182"/>
-      <c r="D12" s="183"/>
-      <c r="E12" s="183"/>
-      <c r="F12" s="184"/>
-    </row>
-    <row r="13" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="27"/>
-      <c r="B13" s="28">
+      <c r="C12" s="168"/>
+      <c r="D12" s="169"/>
+      <c r="E12" s="169"/>
+      <c r="F12" s="170"/>
+      <c r="G12" s="28"/>
+    </row>
+    <row r="13" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="29"/>
+      <c r="B13" s="30">
         <v>3</v>
       </c>
-      <c r="C13" s="189" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="190"/>
-      <c r="E13" s="190"/>
-      <c r="F13" s="191"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="29"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="192"/>
-      <c r="D14" s="193"/>
-      <c r="E14" s="193"/>
-      <c r="F14" s="194"/>
-    </row>
-    <row r="15" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="32">
+      <c r="C13" s="175" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="176"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="177"/>
+      <c r="G13" s="28"/>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="31"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="178"/>
+      <c r="D14" s="179"/>
+      <c r="E14" s="179"/>
+      <c r="F14" s="180"/>
+      <c r="G14" s="78"/>
+    </row>
+    <row r="15" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="34">
         <v>1</v>
       </c>
-      <c r="C15" s="195" t="s">
-        <v>75</v>
-      </c>
-      <c r="D15" s="196"/>
-      <c r="E15" s="196"/>
-      <c r="F15" s="197"/>
-    </row>
-    <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="27"/>
-      <c r="B16" s="28">
+      <c r="C15" s="181" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" s="182"/>
+      <c r="E15" s="182"/>
+      <c r="F15" s="183"/>
+      <c r="G15" s="80" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="29"/>
+      <c r="B16" s="30">
         <v>2</v>
       </c>
-      <c r="C16" s="113" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" s="114"/>
-      <c r="E16" s="114"/>
-      <c r="F16" s="115"/>
-    </row>
-    <row r="17" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="27"/>
-      <c r="B17" s="28">
+      <c r="C16" s="126" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" s="127"/>
+      <c r="E16" s="127"/>
+      <c r="F16" s="128"/>
+      <c r="G16" s="82" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="29"/>
+      <c r="B17" s="30">
         <v>3</v>
       </c>
-      <c r="C17" s="135" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="137"/>
-    </row>
-    <row r="18" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="33"/>
-      <c r="B18" s="30">
+      <c r="C17" s="120" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="122"/>
+      <c r="G17" s="87" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="35"/>
+      <c r="B18" s="32">
         <v>4</v>
       </c>
-      <c r="C18" s="174"/>
-      <c r="D18" s="175"/>
-      <c r="E18" s="175"/>
-      <c r="F18" s="176"/>
-    </row>
-    <row r="19" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="32">
+      <c r="C18" s="193"/>
+      <c r="D18" s="194"/>
+      <c r="E18" s="194"/>
+      <c r="F18" s="195"/>
+      <c r="G18" s="78"/>
+    </row>
+    <row r="19" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="34">
         <v>1</v>
       </c>
-      <c r="C19" s="179" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" s="180"/>
-      <c r="E19" s="180"/>
-      <c r="F19" s="181"/>
-    </row>
-    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="27"/>
-      <c r="B20" s="28">
+      <c r="C19" s="198" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" s="199"/>
+      <c r="E19" s="199"/>
+      <c r="F19" s="200"/>
+      <c r="G19" s="85" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="29"/>
+      <c r="B20" s="30">
         <v>2</v>
       </c>
-      <c r="C20" s="113" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="177"/>
-      <c r="E20" s="178" t="s">
-        <v>79</v>
-      </c>
-      <c r="F20" s="115"/>
-    </row>
-    <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="27"/>
-      <c r="B21" s="28">
+      <c r="C20" s="126" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="196"/>
+      <c r="E20" s="197" t="s">
+        <v>109</v>
+      </c>
+      <c r="F20" s="128"/>
+      <c r="G20" s="79" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="29"/>
+      <c r="B21" s="30">
         <v>3</v>
       </c>
-      <c r="C21" s="156"/>
-      <c r="D21" s="157"/>
-      <c r="E21" s="157"/>
-      <c r="F21" s="158"/>
-    </row>
-    <row r="22" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="33"/>
-      <c r="B22" s="30">
+      <c r="C21" s="184"/>
+      <c r="D21" s="185"/>
+      <c r="E21" s="185"/>
+      <c r="F21" s="186"/>
+      <c r="G21" s="82"/>
+    </row>
+    <row r="22" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="35"/>
+      <c r="B22" s="32">
         <v>4</v>
       </c>
-      <c r="C22" s="162"/>
-      <c r="D22" s="163"/>
-      <c r="E22" s="163"/>
-      <c r="F22" s="164"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="32">
+      <c r="C22" s="187"/>
+      <c r="D22" s="188"/>
+      <c r="E22" s="188"/>
+      <c r="F22" s="189"/>
+      <c r="G22" s="54"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="34">
         <v>1</v>
       </c>
-      <c r="C23" s="171"/>
-      <c r="D23" s="172"/>
-      <c r="E23" s="172"/>
-      <c r="F23" s="173"/>
-    </row>
-    <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="27"/>
-      <c r="B24" s="28">
+      <c r="C23" s="165"/>
+      <c r="D23" s="166"/>
+      <c r="E23" s="166"/>
+      <c r="F23" s="167"/>
+      <c r="G23" s="64"/>
+    </row>
+    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="29"/>
+      <c r="B24" s="30">
         <v>2</v>
       </c>
-      <c r="C24" s="168"/>
-      <c r="D24" s="169"/>
-      <c r="E24" s="169"/>
-      <c r="F24" s="170"/>
-    </row>
-    <row r="25" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="33"/>
-      <c r="B25" s="30">
+      <c r="C24" s="190"/>
+      <c r="D24" s="191"/>
+      <c r="E24" s="191"/>
+      <c r="F24" s="192"/>
+      <c r="G24" s="82"/>
+    </row>
+    <row r="25" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="35"/>
+      <c r="B25" s="32">
         <v>3</v>
       </c>
-      <c r="C25" s="144" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="145"/>
-      <c r="E25" s="145"/>
-      <c r="F25" s="146"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="32">
+      <c r="C25" s="204" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="205"/>
+      <c r="E25" s="205"/>
+      <c r="F25" s="206"/>
+      <c r="G25" s="54"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="34">
         <v>2</v>
       </c>
-      <c r="C26" s="147"/>
-      <c r="D26" s="148"/>
-      <c r="E26" s="148"/>
-      <c r="F26" s="149"/>
-    </row>
-    <row r="27" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="34"/>
-      <c r="B27" s="28">
+      <c r="C26" s="207"/>
+      <c r="D26" s="208"/>
+      <c r="E26" s="208"/>
+      <c r="F26" s="209"/>
+      <c r="G26" s="64"/>
+    </row>
+    <row r="27" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="36"/>
+      <c r="B27" s="30">
         <v>3</v>
       </c>
-      <c r="C27" s="82" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" s="83"/>
-      <c r="E27" s="83"/>
-      <c r="F27" s="84"/>
-    </row>
-    <row r="28" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="34"/>
-      <c r="B28" s="28">
+      <c r="C27" s="102" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="103"/>
+      <c r="E27" s="103"/>
+      <c r="F27" s="104"/>
+      <c r="G27" s="79" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="36"/>
+      <c r="B28" s="30">
         <v>4</v>
       </c>
-      <c r="C28" s="82" t="s">
-        <v>85</v>
-      </c>
-      <c r="D28" s="83"/>
-      <c r="E28" s="83"/>
-      <c r="F28" s="84"/>
-    </row>
-    <row r="29" spans="1:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="36"/>
-      <c r="B29" s="30">
+      <c r="C28" s="102" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" s="103"/>
+      <c r="E28" s="103"/>
+      <c r="F28" s="104"/>
+      <c r="G28" s="79" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="38"/>
+      <c r="B29" s="32">
         <v>5</v>
       </c>
-      <c r="C29" s="159" t="s">
-        <v>87</v>
-      </c>
-      <c r="D29" s="160"/>
-      <c r="E29" s="160"/>
-      <c r="F29" s="161"/>
-    </row>
-    <row r="30" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" s="32">
+      <c r="C29" s="216" t="s">
+        <v>121</v>
+      </c>
+      <c r="D29" s="217"/>
+      <c r="E29" s="217"/>
+      <c r="F29" s="218"/>
+      <c r="G29" s="84" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="34">
         <v>1</v>
       </c>
-      <c r="C30" s="150" t="s">
-        <v>107</v>
-      </c>
-      <c r="D30" s="151"/>
-      <c r="E30" s="151"/>
-      <c r="F30" s="152"/>
-    </row>
-    <row r="31" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="38"/>
-      <c r="B31" s="28">
+      <c r="C30" s="210" t="s">
+        <v>143</v>
+      </c>
+      <c r="D30" s="211"/>
+      <c r="E30" s="211"/>
+      <c r="F30" s="212"/>
+      <c r="G30" s="85" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="40"/>
+      <c r="B31" s="30">
         <v>2</v>
       </c>
-      <c r="C31" s="113" t="s">
-        <v>108</v>
-      </c>
-      <c r="D31" s="114"/>
-      <c r="E31" s="114"/>
-      <c r="F31" s="115"/>
-    </row>
-    <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="39"/>
-      <c r="B32" s="35">
+      <c r="C31" s="126" t="s">
+        <v>144</v>
+      </c>
+      <c r="D31" s="127"/>
+      <c r="E31" s="127"/>
+      <c r="F31" s="128"/>
+      <c r="G31" s="82" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="41"/>
+      <c r="B32" s="37">
         <v>3</v>
       </c>
-      <c r="C32" s="156"/>
-      <c r="D32" s="157"/>
-      <c r="E32" s="157"/>
-      <c r="F32" s="158"/>
-    </row>
-    <row r="33" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="40"/>
-      <c r="B33" s="30">
+      <c r="C32" s="184"/>
+      <c r="D32" s="185"/>
+      <c r="E32" s="185"/>
+      <c r="F32" s="186"/>
+      <c r="G32" s="70"/>
+    </row>
+    <row r="33" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="42"/>
+      <c r="B33" s="32">
         <v>4</v>
       </c>
-      <c r="C33" s="162"/>
-      <c r="D33" s="163"/>
-      <c r="E33" s="163"/>
-      <c r="F33" s="164"/>
-    </row>
-    <row r="34" spans="1:6" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="41"/>
-      <c r="B34" s="42"/>
-      <c r="C34" s="153"/>
-      <c r="D34" s="154"/>
-      <c r="E34" s="154"/>
-      <c r="F34" s="155"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="43"/>
-      <c r="B35" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="C35" s="165" t="s">
-        <v>74</v>
-      </c>
-      <c r="D35" s="166"/>
-      <c r="E35" s="166"/>
-      <c r="F35" s="167"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="51"/>
-      <c r="B36" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="C36" s="113" t="s">
-        <v>35</v>
-      </c>
-      <c r="D36" s="114"/>
-      <c r="E36" s="114"/>
-      <c r="F36" s="115"/>
-    </row>
-    <row r="37" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="52"/>
-      <c r="B37" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="141" t="s">
-        <v>34</v>
-      </c>
-      <c r="D37" s="142"/>
-      <c r="E37" s="142"/>
-      <c r="F37" s="143"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C33" s="187"/>
+      <c r="D33" s="188"/>
+      <c r="E33" s="188"/>
+      <c r="F33" s="189"/>
+      <c r="G33" s="54"/>
+    </row>
+    <row r="34" spans="1:7" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="43"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="213"/>
+      <c r="D34" s="214"/>
+      <c r="E34" s="214"/>
+      <c r="F34" s="215"/>
+      <c r="G34" s="55"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="46"/>
+      <c r="B35" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="219" t="s">
+        <v>98</v>
+      </c>
+      <c r="D35" s="220"/>
+      <c r="E35" s="220"/>
+      <c r="F35" s="221"/>
+      <c r="G35" s="86" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="56"/>
+      <c r="B36" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="126" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" s="127"/>
+      <c r="E36" s="127"/>
+      <c r="F36" s="128"/>
+      <c r="G36" s="79" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="57"/>
+      <c r="B37" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="201" t="s">
+        <v>37</v>
+      </c>
+      <c r="D37" s="202"/>
+      <c r="E37" s="202"/>
+      <c r="F37" s="203"/>
+      <c r="G37" s="84" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="C19:F19"/>
     <mergeCell ref="C37:F37"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C26:F26"/>
@@ -3290,6 +3666,25 @@
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -3320,7 +3715,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3329,78 +3724,79 @@
     <col min="4" max="4" width="20.42578125" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.85546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="67" t="s">
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="76" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="67" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="76" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="66"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="67" t="s">
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="76" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="68" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F4" s="77" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -3410,46 +3806,46 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="203" t="s">
+    <row r="7" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="250" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="203"/>
-      <c r="E7" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="54" t="s">
+      <c r="D7" s="250"/>
+      <c r="E7" s="58" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="59" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="186" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="186"/>
-      <c r="E8" s="186"/>
-      <c r="F8" s="186"/>
-    </row>
-    <row r="9" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+        <v>26</v>
+      </c>
+      <c r="C8" s="172" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="172"/>
+      <c r="E8" s="172"/>
+      <c r="F8" s="172"/>
+    </row>
+    <row r="9" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="208" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" s="208"/>
-      <c r="E9" s="208"/>
-      <c r="F9" s="208"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>33</v>
+      </c>
+      <c r="C9" s="255" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="255"/>
+      <c r="E9" s="255"/>
+      <c r="F9" s="255"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="20" t="s">
         <v>0</v>
@@ -3460,348 +3856,395 @@
       <c r="D10" s="22"/>
       <c r="E10" s="23"/>
       <c r="F10" s="24"/>
-    </row>
-    <row r="11" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="26">
+      <c r="G10" s="25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="27">
         <v>3</v>
       </c>
-      <c r="C11" s="205" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" s="206"/>
-      <c r="E11" s="206"/>
-      <c r="F11" s="207"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28">
+      <c r="C11" s="252" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" s="253"/>
+      <c r="E11" s="253"/>
+      <c r="F11" s="254"/>
+      <c r="G11" s="80" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="29"/>
+      <c r="B12" s="30">
         <v>4</v>
       </c>
-      <c r="C12" s="189" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" s="190"/>
-      <c r="E12" s="190"/>
-      <c r="F12" s="191"/>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="27"/>
-      <c r="B13" s="28">
+      <c r="C12" s="175" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" s="176"/>
+      <c r="E12" s="176"/>
+      <c r="F12" s="177"/>
+      <c r="G12" s="79" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="29"/>
+      <c r="B13" s="30">
         <v>5</v>
       </c>
-      <c r="C13" s="189" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" s="190"/>
-      <c r="E13" s="190"/>
-      <c r="F13" s="191"/>
-    </row>
-    <row r="14" spans="1:6" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="32" t="s">
+      <c r="C13" s="175" t="s">
+        <v>115</v>
+      </c>
+      <c r="D13" s="176"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="177"/>
+      <c r="G13" s="79" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="251" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="163"/>
+      <c r="E14" s="163"/>
+      <c r="F14" s="164"/>
+      <c r="G14" s="64"/>
+    </row>
+    <row r="15" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="29"/>
+      <c r="B15" s="30">
+        <v>4</v>
+      </c>
+      <c r="C15" s="157" t="s">
+        <v>116</v>
+      </c>
+      <c r="D15" s="158"/>
+      <c r="E15" s="158"/>
+      <c r="F15" s="159"/>
+      <c r="G15" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="204" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="100"/>
-      <c r="E14" s="100"/>
-      <c r="F14" s="101"/>
-    </row>
-    <row r="15" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="27"/>
-      <c r="B15" s="28">
+    </row>
+    <row r="16" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="29"/>
+      <c r="B16" s="30">
+        <v>5</v>
+      </c>
+      <c r="C16" s="126" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="127"/>
+      <c r="E16" s="127"/>
+      <c r="F16" s="128"/>
+      <c r="G16" s="79" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="35"/>
+      <c r="B17" s="32">
+        <v>6</v>
+      </c>
+      <c r="C17" s="256" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" s="257"/>
+      <c r="E17" s="257"/>
+      <c r="F17" s="258"/>
+      <c r="G17" s="84" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="34">
+        <v>1</v>
+      </c>
+      <c r="C18" s="259"/>
+      <c r="D18" s="260"/>
+      <c r="E18" s="260"/>
+      <c r="F18" s="261"/>
+      <c r="G18" s="82"/>
+    </row>
+    <row r="19" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="29"/>
+      <c r="B19" s="30">
+        <v>2</v>
+      </c>
+      <c r="C19" s="245"/>
+      <c r="D19" s="246"/>
+      <c r="E19" s="247" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="248"/>
+      <c r="G19" s="79" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="29"/>
+      <c r="B20" s="30">
+        <v>3</v>
+      </c>
+      <c r="C20" s="102" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="103"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="104"/>
+      <c r="G20" s="79" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="35"/>
+      <c r="B21" s="32">
         <v>4</v>
       </c>
-      <c r="C15" s="92" t="s">
-        <v>83</v>
-      </c>
-      <c r="D15" s="93"/>
-      <c r="E15" s="93"/>
-      <c r="F15" s="94"/>
-    </row>
-    <row r="16" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="27"/>
-      <c r="B16" s="28">
+      <c r="C21" s="222"/>
+      <c r="D21" s="223"/>
+      <c r="E21" s="223"/>
+      <c r="F21" s="224"/>
+      <c r="G21" s="78"/>
+    </row>
+    <row r="22" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="34">
+        <v>2</v>
+      </c>
+      <c r="C22" s="225" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" s="226"/>
+      <c r="E22" s="226"/>
+      <c r="F22" s="227"/>
+      <c r="G22" s="85" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="29"/>
+      <c r="B23" s="30">
+        <v>3</v>
+      </c>
+      <c r="C23" s="175" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" s="176"/>
+      <c r="E23" s="176"/>
+      <c r="F23" s="177"/>
+      <c r="G23" s="79" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="29"/>
+      <c r="B24" s="30">
+        <v>4</v>
+      </c>
+      <c r="C24" s="157" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="158"/>
+      <c r="E24" s="158"/>
+      <c r="F24" s="159"/>
+      <c r="G24" s="79" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="35"/>
+      <c r="B25" s="32">
         <v>5</v>
       </c>
-      <c r="C16" s="113" t="s">
+      <c r="C25" s="216"/>
+      <c r="D25" s="217"/>
+      <c r="E25" s="217"/>
+      <c r="F25" s="218"/>
+      <c r="G25" s="89"/>
+    </row>
+    <row r="26" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="34">
+        <v>3</v>
+      </c>
+      <c r="C26" s="231"/>
+      <c r="D26" s="232"/>
+      <c r="E26" s="232"/>
+      <c r="F26" s="233"/>
+      <c r="G26" s="88"/>
+    </row>
+    <row r="27" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="36"/>
+      <c r="B27" s="30">
+        <v>4</v>
+      </c>
+      <c r="C27" s="126" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" s="127"/>
+      <c r="E27" s="127"/>
+      <c r="F27" s="128"/>
+      <c r="G27" s="82" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="36"/>
+      <c r="B28" s="30">
+        <v>5</v>
+      </c>
+      <c r="C28" s="126" t="s">
+        <v>122</v>
+      </c>
+      <c r="D28" s="127"/>
+      <c r="E28" s="127"/>
+      <c r="F28" s="128"/>
+      <c r="G28" s="82" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="38"/>
+      <c r="B29" s="32">
+        <v>6</v>
+      </c>
+      <c r="C29" s="234" t="s">
+        <v>123</v>
+      </c>
+      <c r="D29" s="235"/>
+      <c r="E29" s="235"/>
+      <c r="F29" s="236"/>
+      <c r="G29" s="89" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="34">
+        <v>2</v>
+      </c>
+      <c r="C30" s="237" t="s">
+        <v>124</v>
+      </c>
+      <c r="D30" s="238"/>
+      <c r="E30" s="238"/>
+      <c r="F30" s="239"/>
+      <c r="G30" s="88" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="40"/>
+      <c r="B31" s="30">
+        <v>3</v>
+      </c>
+      <c r="C31" s="126" t="s">
+        <v>125</v>
+      </c>
+      <c r="D31" s="240"/>
+      <c r="E31" s="240"/>
+      <c r="F31" s="241"/>
+      <c r="G31" s="82" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="41"/>
+      <c r="B32" s="37">
+        <v>4</v>
+      </c>
+      <c r="C32" s="184"/>
+      <c r="D32" s="185"/>
+      <c r="E32" s="185"/>
+      <c r="F32" s="186"/>
+      <c r="G32" s="70"/>
+    </row>
+    <row r="33" spans="1:7" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="42"/>
+      <c r="B33" s="32">
+        <v>5</v>
+      </c>
+      <c r="C33" s="187"/>
+      <c r="D33" s="188"/>
+      <c r="E33" s="188"/>
+      <c r="F33" s="189"/>
+      <c r="G33" s="54"/>
+    </row>
+    <row r="34" spans="1:7" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="65"/>
+      <c r="B34" s="66"/>
+      <c r="C34" s="242"/>
+      <c r="D34" s="243"/>
+      <c r="E34" s="243"/>
+      <c r="F34" s="244"/>
+      <c r="G34" s="67"/>
+    </row>
+    <row r="35" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="68"/>
+      <c r="B35" s="69" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="228" t="s">
+        <v>48</v>
+      </c>
+      <c r="D35" s="229"/>
+      <c r="E35" s="229"/>
+      <c r="F35" s="230"/>
+      <c r="G35" s="90" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="114"/>
-      <c r="E16" s="114"/>
-      <c r="F16" s="115"/>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="33"/>
-      <c r="B17" s="30">
-        <v>6</v>
-      </c>
-      <c r="C17" s="209" t="s">
-        <v>94</v>
-      </c>
-      <c r="D17" s="210"/>
-      <c r="E17" s="210"/>
-      <c r="F17" s="211"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="32">
-        <v>1</v>
-      </c>
-      <c r="C18" s="212"/>
-      <c r="D18" s="213"/>
-      <c r="E18" s="213"/>
-      <c r="F18" s="214"/>
-    </row>
-    <row r="19" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="27"/>
-      <c r="B19" s="28">
-        <v>2</v>
-      </c>
-      <c r="C19" s="198"/>
-      <c r="D19" s="199"/>
-      <c r="E19" s="200" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" s="201"/>
-    </row>
-    <row r="20" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="27"/>
-      <c r="B20" s="28">
-        <v>3</v>
-      </c>
-      <c r="C20" s="82" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="83"/>
-      <c r="E20" s="83"/>
-      <c r="F20" s="84"/>
-    </row>
-    <row r="21" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="33"/>
-      <c r="B21" s="30">
-        <v>4</v>
-      </c>
-      <c r="C21" s="215"/>
-      <c r="D21" s="216"/>
-      <c r="E21" s="216"/>
-      <c r="F21" s="217"/>
-    </row>
-    <row r="22" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="32">
-        <v>2</v>
-      </c>
-      <c r="C22" s="218" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" s="219"/>
-      <c r="E22" s="219"/>
-      <c r="F22" s="220"/>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="27"/>
-      <c r="B23" s="28">
-        <v>3</v>
-      </c>
-      <c r="C23" s="189" t="s">
-        <v>92</v>
-      </c>
-      <c r="D23" s="190"/>
-      <c r="E23" s="190"/>
-      <c r="F23" s="191"/>
-    </row>
-    <row r="24" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="27"/>
-      <c r="B24" s="28">
-        <v>4</v>
-      </c>
-      <c r="C24" s="92" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" s="93"/>
-      <c r="E24" s="93"/>
-      <c r="F24" s="94"/>
-    </row>
-    <row r="25" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="33"/>
-      <c r="B25" s="30">
-        <v>5</v>
-      </c>
-      <c r="C25" s="159"/>
-      <c r="D25" s="160"/>
-      <c r="E25" s="160"/>
-      <c r="F25" s="161"/>
-    </row>
-    <row r="26" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="32">
-        <v>3</v>
-      </c>
-      <c r="C26" s="224"/>
-      <c r="D26" s="225"/>
-      <c r="E26" s="225"/>
-      <c r="F26" s="226"/>
-    </row>
-    <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="34"/>
-      <c r="B27" s="28">
-        <v>4</v>
-      </c>
-      <c r="C27" s="113" t="s">
-        <v>86</v>
-      </c>
-      <c r="D27" s="114"/>
-      <c r="E27" s="114"/>
-      <c r="F27" s="115"/>
-    </row>
-    <row r="28" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="34"/>
-      <c r="B28" s="28">
-        <v>5</v>
-      </c>
-      <c r="C28" s="113" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" s="114"/>
-      <c r="E28" s="114"/>
-      <c r="F28" s="115"/>
-    </row>
-    <row r="29" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="36"/>
-      <c r="B29" s="30">
-        <v>6</v>
-      </c>
-      <c r="C29" s="227" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29" s="228"/>
-      <c r="E29" s="228"/>
-      <c r="F29" s="229"/>
-    </row>
-    <row r="30" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" s="32">
-        <v>2</v>
-      </c>
-      <c r="C30" s="230" t="s">
-        <v>90</v>
-      </c>
-      <c r="D30" s="231"/>
-      <c r="E30" s="231"/>
-      <c r="F30" s="232"/>
-    </row>
-    <row r="31" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="38"/>
-      <c r="B31" s="28">
-        <v>3</v>
-      </c>
-      <c r="C31" s="113" t="s">
-        <v>91</v>
-      </c>
-      <c r="D31" s="233"/>
-      <c r="E31" s="233"/>
-      <c r="F31" s="234"/>
-    </row>
-    <row r="32" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="39"/>
-      <c r="B32" s="35">
-        <v>4</v>
-      </c>
-      <c r="C32" s="156"/>
-      <c r="D32" s="157"/>
-      <c r="E32" s="157"/>
-      <c r="F32" s="158"/>
-    </row>
-    <row r="33" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="40"/>
-      <c r="B33" s="30">
-        <v>5</v>
-      </c>
-      <c r="C33" s="162"/>
-      <c r="D33" s="163"/>
-      <c r="E33" s="163"/>
-      <c r="F33" s="164"/>
-    </row>
-    <row r="34" spans="1:6" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="59"/>
-      <c r="B34" s="60"/>
-      <c r="C34" s="235"/>
-      <c r="D34" s="236"/>
-      <c r="E34" s="236"/>
-      <c r="F34" s="237"/>
-    </row>
-    <row r="35" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="61"/>
-      <c r="B35" s="62" t="s">
-        <v>30</v>
-      </c>
-      <c r="C35" s="221" t="s">
-        <v>38</v>
-      </c>
-      <c r="D35" s="222"/>
-      <c r="E35" s="222"/>
-      <c r="F35" s="223"/>
-    </row>
-    <row r="36" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="64"/>
-      <c r="C36" s="202" t="s">
-        <v>43</v>
-      </c>
-      <c r="D36" s="202"/>
-      <c r="E36" s="202"/>
-      <c r="F36" s="202"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="36" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="72" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="73"/>
+      <c r="C36" s="249" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" s="249"/>
+      <c r="E36" s="249"/>
+      <c r="F36" s="249"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F34"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="E19:F19"/>
@@ -3818,6 +4261,21 @@
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C34:F34"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -3855,7 +4313,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3864,10 +4322,11 @@
     <col min="4" max="4" width="20.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.5703125" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.85546875" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -3875,15 +4334,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -3891,39 +4350,39 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -3933,46 +4392,46 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="250" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="296" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="250"/>
+      <c r="D7" s="296"/>
       <c r="E7" s="15" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="186" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="186"/>
-      <c r="E8" s="186"/>
-      <c r="F8" s="186"/>
-    </row>
-    <row r="9" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+        <v>26</v>
+      </c>
+      <c r="C8" s="172" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="172"/>
+      <c r="E8" s="172"/>
+      <c r="F8" s="172"/>
+    </row>
+    <row r="9" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
     </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="20" t="s">
         <v>0</v>
@@ -3983,315 +4442,394 @@
       <c r="D10" s="22"/>
       <c r="E10" s="23"/>
       <c r="F10" s="24"/>
-    </row>
-    <row r="11" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="26">
+      <c r="G10" s="25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="27">
         <v>1</v>
       </c>
-      <c r="C11" s="257"/>
-      <c r="D11" s="258"/>
-      <c r="E11" s="206" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="207"/>
-    </row>
-    <row r="12" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28">
+      <c r="C11" s="300"/>
+      <c r="D11" s="301"/>
+      <c r="E11" s="253" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="254"/>
+      <c r="G11" s="80" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="29"/>
+      <c r="B12" s="30">
         <v>2</v>
       </c>
-      <c r="C12" s="126" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12" s="127"/>
-      <c r="E12" s="127"/>
-      <c r="F12" s="128"/>
-    </row>
-    <row r="13" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="27"/>
-      <c r="B13" s="28">
+      <c r="C12" s="111" t="s">
+        <v>132</v>
+      </c>
+      <c r="D12" s="112"/>
+      <c r="E12" s="112"/>
+      <c r="F12" s="113"/>
+      <c r="G12" s="87" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="29"/>
+      <c r="B13" s="30">
         <v>3</v>
       </c>
-      <c r="C13" s="254" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" s="255"/>
-      <c r="E13" s="255"/>
-      <c r="F13" s="256"/>
-    </row>
-    <row r="14" spans="1:6" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="27"/>
-      <c r="B14" s="28">
+      <c r="C13" s="293" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" s="294"/>
+      <c r="E13" s="294"/>
+      <c r="F13" s="295"/>
+      <c r="G13" s="87" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="29"/>
+      <c r="B14" s="30">
         <v>4</v>
       </c>
-      <c r="C14" s="259" t="s">
-        <v>98</v>
-      </c>
-      <c r="D14" s="260"/>
-      <c r="E14" s="261"/>
-      <c r="F14" s="262"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="32">
+      <c r="C14" s="302" t="s">
+        <v>134</v>
+      </c>
+      <c r="D14" s="303"/>
+      <c r="E14" s="304"/>
+      <c r="F14" s="305"/>
+      <c r="G14" s="92" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="34">
         <v>2</v>
       </c>
-      <c r="C15" s="251"/>
-      <c r="D15" s="252"/>
-      <c r="E15" s="252"/>
-      <c r="F15" s="253"/>
-    </row>
-    <row r="16" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="27"/>
-      <c r="B16" s="28">
+      <c r="C15" s="297"/>
+      <c r="D15" s="298"/>
+      <c r="E15" s="298"/>
+      <c r="F15" s="299"/>
+      <c r="G15" s="71"/>
+    </row>
+    <row r="16" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="29"/>
+      <c r="B16" s="30">
         <v>3</v>
       </c>
-      <c r="C16" s="126" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" s="127"/>
-      <c r="E16" s="127"/>
-      <c r="F16" s="128"/>
-    </row>
-    <row r="17" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="27"/>
-      <c r="B17" s="28">
+      <c r="C16" s="111" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="112"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="113"/>
+      <c r="G16" s="87" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="29"/>
+      <c r="B17" s="30">
         <v>4</v>
       </c>
-      <c r="C17" s="241" t="s">
-        <v>99</v>
-      </c>
-      <c r="D17" s="242"/>
-      <c r="E17" s="242"/>
-      <c r="F17" s="243"/>
-    </row>
-    <row r="18" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="27"/>
-      <c r="B18" s="28">
+      <c r="C17" s="281" t="s">
+        <v>135</v>
+      </c>
+      <c r="D17" s="282"/>
+      <c r="E17" s="282"/>
+      <c r="F17" s="309"/>
+      <c r="G17" s="87" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="29"/>
+      <c r="B18" s="30">
         <v>5</v>
       </c>
-      <c r="C18" s="241" t="s">
-        <v>95</v>
-      </c>
-      <c r="D18" s="242"/>
-      <c r="E18" s="263"/>
-      <c r="F18" s="264"/>
-    </row>
-    <row r="19" spans="1:6" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="33"/>
-      <c r="B19" s="30">
+      <c r="C18" s="281" t="s">
+        <v>129</v>
+      </c>
+      <c r="D18" s="282"/>
+      <c r="E18" s="262"/>
+      <c r="F18" s="263"/>
+      <c r="G18" s="87" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="35"/>
+      <c r="B19" s="32">
         <v>6</v>
       </c>
-      <c r="C19" s="282"/>
-      <c r="D19" s="283"/>
-      <c r="E19" s="265"/>
-      <c r="F19" s="266"/>
-    </row>
-    <row r="20" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="32">
+      <c r="C19" s="283"/>
+      <c r="D19" s="284"/>
+      <c r="E19" s="264"/>
+      <c r="F19" s="265"/>
+      <c r="G19" s="91" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="34">
         <v>1</v>
       </c>
-      <c r="C20" s="244"/>
-      <c r="D20" s="245"/>
-      <c r="E20" s="245"/>
-      <c r="F20" s="246"/>
-    </row>
-    <row r="21" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="27"/>
-      <c r="B21" s="28">
+      <c r="C20" s="310"/>
+      <c r="D20" s="311"/>
+      <c r="E20" s="311"/>
+      <c r="F20" s="312"/>
+      <c r="G20" s="87"/>
+    </row>
+    <row r="21" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="29"/>
+      <c r="B21" s="30">
         <v>2</v>
       </c>
-      <c r="C21" s="241" t="s">
-        <v>109</v>
-      </c>
-      <c r="D21" s="242"/>
-      <c r="E21" s="242"/>
-      <c r="F21" s="243"/>
-    </row>
-    <row r="22" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="27"/>
-      <c r="B22" s="28">
+      <c r="C21" s="281" t="s">
+        <v>145</v>
+      </c>
+      <c r="D21" s="282"/>
+      <c r="E21" s="282"/>
+      <c r="F21" s="309"/>
+      <c r="G21" s="87" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="29"/>
+      <c r="B22" s="30">
         <v>3</v>
       </c>
-      <c r="C22" s="247" t="s">
-        <v>110</v>
-      </c>
-      <c r="D22" s="248"/>
-      <c r="E22" s="248"/>
-      <c r="F22" s="249"/>
-    </row>
-    <row r="23" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="27"/>
-      <c r="B23" s="28">
+      <c r="C22" s="313" t="s">
+        <v>146</v>
+      </c>
+      <c r="D22" s="314"/>
+      <c r="E22" s="314"/>
+      <c r="F22" s="315"/>
+      <c r="G22" s="87" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="29"/>
+      <c r="B23" s="30">
         <v>4</v>
       </c>
-      <c r="C23" s="273"/>
-      <c r="D23" s="274"/>
-      <c r="E23" s="274"/>
-      <c r="F23" s="275"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A24" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="32">
+      <c r="C23" s="272"/>
+      <c r="D23" s="273"/>
+      <c r="E23" s="273"/>
+      <c r="F23" s="274"/>
+      <c r="G23" s="87"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="34">
         <v>1</v>
       </c>
-      <c r="C24" s="238" t="s">
-        <v>100</v>
-      </c>
-      <c r="D24" s="239"/>
-      <c r="E24" s="239"/>
-      <c r="F24" s="240"/>
-    </row>
-    <row r="25" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="27"/>
-      <c r="B25" s="28">
+      <c r="C24" s="306" t="s">
+        <v>136</v>
+      </c>
+      <c r="D24" s="307"/>
+      <c r="E24" s="307"/>
+      <c r="F24" s="308"/>
+      <c r="G24" s="86" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="29"/>
+      <c r="B25" s="30">
         <v>2</v>
       </c>
-      <c r="C25" s="76" t="s">
-        <v>101</v>
-      </c>
-      <c r="D25" s="77"/>
-      <c r="E25" s="77"/>
-      <c r="F25" s="78"/>
-    </row>
-    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="27"/>
-      <c r="B26" s="28">
+      <c r="C25" s="144" t="s">
+        <v>137</v>
+      </c>
+      <c r="D25" s="145"/>
+      <c r="E25" s="145"/>
+      <c r="F25" s="146"/>
+      <c r="G25" s="87" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="29"/>
+      <c r="B26" s="30">
         <v>3</v>
       </c>
-      <c r="C26" s="254" t="s">
-        <v>101</v>
-      </c>
-      <c r="D26" s="255"/>
-      <c r="E26" s="255"/>
-      <c r="F26" s="256"/>
-    </row>
-    <row r="27" spans="1:6" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="33"/>
-      <c r="B27" s="30">
+      <c r="C26" s="293" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" s="294"/>
+      <c r="E26" s="294"/>
+      <c r="F26" s="295"/>
+      <c r="G26" s="87" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="35"/>
+      <c r="B27" s="32">
         <v>4</v>
       </c>
-      <c r="C27" s="273" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="274"/>
-      <c r="E27" s="274"/>
-      <c r="F27" s="275"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" s="32">
+      <c r="C27" s="272" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="273"/>
+      <c r="E27" s="273"/>
+      <c r="F27" s="274"/>
+      <c r="G27" s="83" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="34">
         <v>4</v>
       </c>
-      <c r="C28" s="276"/>
-      <c r="D28" s="277"/>
-      <c r="E28" s="277"/>
-      <c r="F28" s="278"/>
-    </row>
-    <row r="29" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="34"/>
-      <c r="B29" s="28">
+      <c r="C28" s="275"/>
+      <c r="D28" s="276"/>
+      <c r="E28" s="276"/>
+      <c r="F28" s="277"/>
+      <c r="G28" s="71"/>
+    </row>
+    <row r="29" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="36"/>
+      <c r="B29" s="30">
         <v>5</v>
       </c>
-      <c r="C29" s="290"/>
-      <c r="D29" s="291"/>
-      <c r="E29" s="127" t="s">
-        <v>102</v>
-      </c>
-      <c r="F29" s="128"/>
-    </row>
-    <row r="30" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="34"/>
-      <c r="B30" s="28">
+      <c r="C29" s="291"/>
+      <c r="D29" s="292"/>
+      <c r="E29" s="112" t="s">
+        <v>138</v>
+      </c>
+      <c r="F29" s="113"/>
+      <c r="G29" s="87" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="36"/>
+      <c r="B30" s="30">
         <v>6</v>
       </c>
-      <c r="C30" s="290"/>
-      <c r="D30" s="291"/>
-      <c r="E30" s="127"/>
-      <c r="F30" s="128"/>
-    </row>
-    <row r="31" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="36"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="279"/>
-      <c r="D31" s="280"/>
-      <c r="E31" s="280"/>
-      <c r="F31" s="281"/>
-    </row>
-    <row r="32" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="55" t="s">
-        <v>24</v>
-      </c>
-      <c r="B32" s="26">
+      <c r="C30" s="291"/>
+      <c r="D30" s="292"/>
+      <c r="E30" s="112"/>
+      <c r="F30" s="113"/>
+      <c r="G30" s="87" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="38"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="278"/>
+      <c r="D31" s="279"/>
+      <c r="E31" s="279"/>
+      <c r="F31" s="280"/>
+      <c r="G31" s="91"/>
+    </row>
+    <row r="32" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="60" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="27">
         <v>4</v>
       </c>
-      <c r="C32" s="284" t="s">
-        <v>103</v>
-      </c>
-      <c r="D32" s="285"/>
-      <c r="E32" s="285"/>
-      <c r="F32" s="286"/>
-    </row>
-    <row r="33" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="38"/>
-      <c r="B33" s="28">
+      <c r="C32" s="285" t="s">
+        <v>139</v>
+      </c>
+      <c r="D32" s="286"/>
+      <c r="E32" s="286"/>
+      <c r="F32" s="287"/>
+      <c r="G32" s="87" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="40"/>
+      <c r="B33" s="30">
         <v>5</v>
       </c>
-      <c r="C33" s="287" t="s">
-        <v>104</v>
-      </c>
-      <c r="D33" s="288"/>
-      <c r="E33" s="288"/>
-      <c r="F33" s="289"/>
-    </row>
-    <row r="34" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="38"/>
-      <c r="B34" s="28">
+      <c r="C33" s="288" t="s">
+        <v>140</v>
+      </c>
+      <c r="D33" s="289"/>
+      <c r="E33" s="289"/>
+      <c r="F33" s="290"/>
+      <c r="G33" s="87" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="40"/>
+      <c r="B34" s="30">
         <v>6</v>
       </c>
-      <c r="C34" s="267"/>
-      <c r="D34" s="268"/>
-      <c r="E34" s="268"/>
-      <c r="F34" s="269"/>
-    </row>
-    <row r="35" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="52"/>
-      <c r="B35" s="56"/>
-      <c r="C35" s="270"/>
-      <c r="D35" s="271"/>
-      <c r="E35" s="271"/>
-      <c r="F35" s="272"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C34" s="266"/>
+      <c r="D34" s="267"/>
+      <c r="E34" s="267"/>
+      <c r="F34" s="268"/>
+      <c r="G34" s="87"/>
+    </row>
+    <row r="35" spans="1:7" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="57"/>
+      <c r="B35" s="61"/>
+      <c r="C35" s="269"/>
+      <c r="D35" s="270"/>
+      <c r="E35" s="270"/>
+      <c r="F35" s="271"/>
+      <c r="G35" s="91"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="E19:F19"/>
@@ -4308,21 +4846,6 @@
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E29:F30"/>
     <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
